--- a/artfynd/A 23935-2025 artfynd.xlsx
+++ b/artfynd/A 23935-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017094</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017091</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017100</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017098</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017101</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017105</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017096</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017086</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017089</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017102</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017097</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017088</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,8 +2063,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017104</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 23935-2025 artfynd.xlsx
+++ b/artfynd/A 23935-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135017094</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135017091</v>
       </c>
       <c r="B3" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135017100</v>
       </c>
       <c r="B4" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135017098</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135017101</v>
       </c>
       <c r="B6" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135017105</v>
       </c>
       <c r="B7" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135017096</v>
       </c>
       <c r="B8" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135017086</v>
       </c>
       <c r="B9" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>135017089</v>
       </c>
       <c r="B10" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>135017102</v>
       </c>
       <c r="B11" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>135017097</v>
       </c>
       <c r="B12" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135017088</v>
       </c>
       <c r="B13" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135017104</v>
       </c>
       <c r="B14" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23935-2025 artfynd.xlsx
+++ b/artfynd/A 23935-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135017094</v>
       </c>
       <c r="B2" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135017091</v>
       </c>
       <c r="B3" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135017100</v>
       </c>
       <c r="B4" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135017098</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135017101</v>
       </c>
       <c r="B6" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135017105</v>
       </c>
       <c r="B7" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135017096</v>
       </c>
       <c r="B8" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135017086</v>
       </c>
       <c r="B9" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>135017089</v>
       </c>
       <c r="B10" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>135017102</v>
       </c>
       <c r="B11" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>135017097</v>
       </c>
       <c r="B12" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135017088</v>
       </c>
       <c r="B13" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135017104</v>
       </c>
       <c r="B14" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
